--- a/artfynd/A 19572-2026 artfynd.xlsx
+++ b/artfynd/A 19572-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>55735268</v>
       </c>
       <c r="B2" t="n">
-        <v>100364</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>103248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>290468.4055132474</v>
+        <v>290468</v>
       </c>
       <c r="R2" t="n">
-        <v>6477394.510458168</v>
+        <v>6477395</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,7 +751,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>OB-Lys-0484</t>
+          <t>Arkiv-OB-Lys-0271</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,19 +759,9 @@
           <t>2015-09-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-09-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,7 +786,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
     </row>
